--- a/Stock Selection/tickers_update.xlsx
+++ b/Stock Selection/tickers_update.xlsx
@@ -438,374 +438,374 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>V</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>INGR</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DUK</t>
+          <t>NVDA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>VHYD.L</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>AEP</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>CIB</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>SQM</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>ASML</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>YPF</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>SMFG</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>FLOA.L</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>LEVI</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>SMFG</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>MAXN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>^VIX</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>VBTC.DE</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BOTZ.L</t>
+          <t>DUK</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>GC=F</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>SPY</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>WMT</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>SHELL.AS</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>APA</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SQM</t>
+          <t>FSLR</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MC.PA</t>
+          <t>PEP</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>KMB</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>MO</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>NEE</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MAXN</t>
+          <t>BOTZ.L</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>TSM</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>MA</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>US30</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SHELL.AS</t>
+          <t>MC.PA</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>VBTC.DE</t>
+          <t>JPY=X</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>AVGO</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>SDIA.L</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>BATT.AS</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>AMAT</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>YUM</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>US30</t>
+          <t>BND</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>BCS</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>GOOGL</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>^VIX</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>VWO</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>DAR</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>MXN=X</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>AAPL</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>JPY=X</t>
+          <t>MSFT</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>EXC</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>AGIO</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>LEVI</t>
+          <t>GILD</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>ACI</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>PANW</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>ING</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>QCOM</t>
         </is>
       </c>
     </row>

--- a/Stock Selection/tickers_update.xlsx
+++ b/Stock Selection/tickers_update.xlsx
@@ -438,49 +438,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>VWO</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>INGR</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>CIB</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>MSFT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>SHELL.AS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>DUK</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SQM</t>
+          <t>MO</t>
         </is>
       </c>
     </row>
@@ -494,31 +490,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>TSM</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MC.PA</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LEVI</t>
+          <t>NVDA</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SMFG</t>
+          <t>PEP</t>
         </is>
       </c>
     </row>
@@ -532,266 +532,266 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>^VIX</t>
+          <t>APA</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>VBTC.DE</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DUK</t>
+          <t>AGIO</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>KMB</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>GOOGL</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>MA</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SHELL.AS</t>
+          <t>EXC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>LEVI</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>BND</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>VHYD.L</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>INGR</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>US30</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>WMT</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BOTZ.L</t>
+          <t>AVGO</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>BCS</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>NEE</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>US30</t>
+          <t>AMAT</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MC.PA</t>
+          <t>YUM</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>JPY=X</t>
+          <t>SDIA.L</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>AEP</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>FLOA.L</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>GILD</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>PANW</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>ACI</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>VBTC.DE</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>YPF</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>GC=F</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>JPY=X</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>DAR</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>SQM</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>V</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>MXN=X</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SPY</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>SMFG</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>FSLR</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>BOTZ.L</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>BATT.AS</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>^VIX</t>
         </is>
       </c>
     </row>

--- a/Stock Selection/tickers_update.xlsx
+++ b/Stock Selection/tickers_update.xlsx
@@ -438,374 +438,374 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>BATT.AS</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BCS</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>AEP</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>EXC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SHELL.AS</t>
+          <t>WMT</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DUK</t>
+          <t>SQM</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>MXN=X</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ASML</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>ACI</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>DAR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MC.PA</t>
+          <t>ING</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>MA</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>DUK</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MAXN</t>
+          <t>AMAT</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>MSFT</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>PEP</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>MC.PA</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>US30</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>TSM</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>MO</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>PANW</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LEVI</t>
+          <t>JPY=X</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>GOOGL</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>^VIX</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>GC=F</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>US30</t>
+          <t>SMFG</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>MAXN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>NEE</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>SHELL.AS</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>YUM</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>VHYD.L</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>CIB</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>AVGO</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>BOTZ.L</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>FSLR</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>BND</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>AAPL</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>VBTC.DE</t>
+          <t>APA</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>GILD</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>SPY</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>JPY=X</t>
+          <t>ASML</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>VBTC.DE</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SQM</t>
+          <t>INGR</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>NVDA</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>YPF</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>KMB</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SMFG</t>
+          <t>LEVI</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>QCOM</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BOTZ.L</t>
+          <t>FLOA.L</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>V</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>^VIX</t>
+          <t>AGIO</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>SDIA.L</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>VWO</t>
         </is>
       </c>
     </row>

--- a/Stock Selection/tickers_update.xlsx
+++ b/Stock Selection/tickers_update.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A55"/>
+  <dimension ref="A1:A57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,185 +438,185 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>AAPL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>PEP</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AEP</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>VBTC.DE</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>INGR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SQM</t>
+          <t>MO</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>AVGO</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BBVA.MC</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>SPY</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>AEP</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>ASML</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>VWO</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DUK</t>
+          <t>MSFT</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>DUK</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>FSLR</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MC.PA</t>
+          <t>MXN=X</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>US30</t>
+          <t>PANW</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>JPY=X</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>APA</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>EXC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>JPY=X</t>
+          <t>MA</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>YPF</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>^VIX</t>
+          <t>SHELL.AS</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>BOTZ.L</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SMFG</t>
+          <t>^VIX</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MAXN</t>
+          <t>GC=F</t>
         </is>
       </c>
     </row>
@@ -630,133 +630,133 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SHELL.AS</t>
+          <t>QCOM</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>SMFG</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>SDIA.L</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>GILD</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>V</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>MC.PA</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BOTZ.L</t>
+          <t>BATT.AS</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>FLOA.L</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>CIB</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>WMT</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>AMAT</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>NVDA</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>BND</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>BAP</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>VBTC.DE</t>
+          <t>AGIO</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>KMB</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>US30</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>BCS</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>GOOGL</t>
         </is>
       </c>
     </row>
@@ -770,42 +770,56 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>MAXN</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>YUM</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>ACI</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>ING</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>TSM</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>VHYD.L</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SQM</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>DAR</t>
         </is>
       </c>
     </row>

--- a/Stock Selection/tickers_update.xlsx
+++ b/Stock Selection/tickers_update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rodwals-my.sharepoint.com/personal/samuel_rodwal_com/Documents/Professional_WorkTools/Github/RodWal-Capital-Insights/Stock Selection/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_08B596FC9C50580F6235547658A886FD9DEB8135" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C896AC6-282C-47FA-B6A5-C3F13ACEE9F6}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_08B59E045E5BCA0E62355476589BBE7AA63F8035" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8E1F2D1-F234-45E0-875F-C861A34BB043}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="615" windowWidth="13920" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,169 +41,169 @@
     <t>Ticker</t>
   </si>
   <si>
+    <t>BND</t>
+  </si>
+  <si>
+    <t>BOTZ.L</t>
+  </si>
+  <si>
+    <t>JPY=X</t>
+  </si>
+  <si>
+    <t>FLOA.L</t>
+  </si>
+  <si>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>VWO</t>
+  </si>
+  <si>
+    <t>KMB</t>
+  </si>
+  <si>
+    <t>BCS</t>
+  </si>
+  <si>
+    <t>DAR</t>
+  </si>
+  <si>
+    <t>VHYD.L</t>
+  </si>
+  <si>
+    <t>LEVI</t>
+  </si>
+  <si>
     <t>WMT</t>
   </si>
   <si>
+    <t>TSM</t>
+  </si>
+  <si>
+    <t>AMAT</t>
+  </si>
+  <si>
+    <t>US30</t>
+  </si>
+  <si>
+    <t>BBVA.MC</t>
+  </si>
+  <si>
+    <t>SDIA.L</t>
+  </si>
+  <si>
+    <t>SPY</t>
+  </si>
+  <si>
+    <t>SHELL.AS</t>
+  </si>
+  <si>
+    <t>DUK</t>
+  </si>
+  <si>
+    <t>QCOM</t>
+  </si>
+  <si>
+    <t>FSLR</t>
+  </si>
+  <si>
+    <t>GILD</t>
+  </si>
+  <si>
+    <t>AVGO</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>YUM</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>INGR</t>
+  </si>
+  <si>
+    <t>CIB</t>
+  </si>
+  <si>
+    <t>GOOGL</t>
+  </si>
+  <si>
+    <t>ING</t>
+  </si>
+  <si>
     <t>ACI</t>
   </si>
   <si>
-    <t>FSLR</t>
-  </si>
-  <si>
-    <t>LEVI</t>
+    <t>MC.PA</t>
+  </si>
+  <si>
+    <t>AEP</t>
+  </si>
+  <si>
+    <t>PANW</t>
+  </si>
+  <si>
+    <t>^VIX</t>
+  </si>
+  <si>
+    <t>PEP</t>
+  </si>
+  <si>
+    <t>BAP</t>
+  </si>
+  <si>
+    <t>YPF</t>
+  </si>
+  <si>
+    <t>VBTC.DE</t>
+  </si>
+  <si>
+    <t>SMFG</t>
+  </si>
+  <si>
+    <t>AAPL</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>GC=F</t>
+  </si>
+  <si>
+    <t>AGIO</t>
+  </si>
+  <si>
+    <t>MSFT</t>
+  </si>
+  <si>
+    <t>MXN=X</t>
+  </si>
+  <si>
+    <t>NEE</t>
+  </si>
+  <si>
+    <t>SQM</t>
   </si>
   <si>
     <t>BATT.AS</t>
   </si>
   <si>
-    <t>SDIA.L</t>
-  </si>
-  <si>
-    <t>AGIO</t>
-  </si>
-  <si>
-    <t>BCS</t>
-  </si>
-  <si>
-    <t>FLOA.L</t>
-  </si>
-  <si>
-    <t>US30</t>
-  </si>
-  <si>
-    <t>NEE</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>AVGO</t>
-  </si>
-  <si>
-    <t>MC.PA</t>
-  </si>
-  <si>
-    <t>TSM</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
     <t>MAXN</t>
   </si>
   <si>
-    <t>SQM</t>
+    <t>EXC</t>
+  </si>
+  <si>
+    <t>MO</t>
+  </si>
+  <si>
+    <t>APA</t>
   </si>
   <si>
     <t>ASML</t>
-  </si>
-  <si>
-    <t>MO</t>
-  </si>
-  <si>
-    <t>MXN=X</t>
-  </si>
-  <si>
-    <t>INGR</t>
-  </si>
-  <si>
-    <t>BAP</t>
-  </si>
-  <si>
-    <t>DUK</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>^VIX</t>
-  </si>
-  <si>
-    <t>AEP</t>
-  </si>
-  <si>
-    <t>AMAT</t>
-  </si>
-  <si>
-    <t>YUM</t>
-  </si>
-  <si>
-    <t>VHYD.L</t>
-  </si>
-  <si>
-    <t>PANW</t>
-  </si>
-  <si>
-    <t>JPY=X</t>
-  </si>
-  <si>
-    <t>BND</t>
-  </si>
-  <si>
-    <t>SHELL.AS</t>
-  </si>
-  <si>
-    <t>DAR</t>
-  </si>
-  <si>
-    <t>CIB</t>
-  </si>
-  <si>
-    <t>EXC</t>
-  </si>
-  <si>
-    <t>SMFG</t>
-  </si>
-  <si>
-    <t>GILD</t>
-  </si>
-  <si>
-    <t>PEP</t>
-  </si>
-  <si>
-    <t>KMB</t>
-  </si>
-  <si>
-    <t>GC=F</t>
-  </si>
-  <si>
-    <t>BBVA.MC</t>
-  </si>
-  <si>
-    <t>VBTC.DE</t>
-  </si>
-  <si>
-    <t>GOOGL</t>
-  </si>
-  <si>
-    <t>APA</t>
-  </si>
-  <si>
-    <t>MSFT</t>
-  </si>
-  <si>
-    <t>SPY</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>BOTZ.L</t>
-  </si>
-  <si>
-    <t>QCOM</t>
-  </si>
-  <si>
-    <t>VWO</t>
-  </si>
-  <si>
-    <t>YPF</t>
-  </si>
-  <si>
-    <t>ING</t>
-  </si>
-  <si>
-    <t>AAPL</t>
   </si>
 </sst>
 </file>
@@ -927,7 +927,7 @@
       </c>
       <c r="B2" t="str">
         <f>VLOOKUP(A2,[1]Sheet1!$C:$C,1,0)</f>
-        <v>WMT</v>
+        <v>BND</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -936,94 +936,88 @@
       </c>
       <c r="B3" t="str">
         <f>VLOOKUP(A3,[1]Sheet1!$C:$C,1,0)</f>
-        <v>ACI</v>
+        <v>BOTZ.L</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" t="e">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
         <f>VLOOKUP(A4,[1]Sheet1!$C:$C,1,0)</f>
-        <v>#N/A</v>
+        <v>JPY=X</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="str">
         <f>VLOOKUP(A5,[1]Sheet1!$C:$C,1,0)</f>
-        <v>FSLR</v>
+        <v>FLOA.L</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" t="str">
         <f>VLOOKUP(A6,[1]Sheet1!$C:$C,1,0)</f>
-        <v>LEVI</v>
+        <v>MA</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="str">
         <f>VLOOKUP(A7,[1]Sheet1!$C:$C,1,0)</f>
-        <v>BATT.AS</v>
+        <v>VWO</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" t="str">
         <f>VLOOKUP(A8,[1]Sheet1!$C:$C,1,0)</f>
-        <v>SDIA.L</v>
+        <v>KMB</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" t="str">
         <f>VLOOKUP(A9,[1]Sheet1!$C:$C,1,0)</f>
-        <v>AGIO</v>
+        <v>BCS</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" t="str">
         <f>VLOOKUP(A10,[1]Sheet1!$C:$C,1,0)</f>
-        <v>BCS</v>
+        <v>DAR</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" t="str">
         <f>VLOOKUP(A11,[1]Sheet1!$C:$C,1,0)</f>
-        <v>FLOA.L</v>
+        <v>VHYD.L</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" t="str">
         <f>VLOOKUP(A12,[1]Sheet1!$C:$C,1,0)</f>
-        <v>US30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" t="str">
-        <f>VLOOKUP(A13,[1]Sheet1!$C:$C,1,0)</f>
-        <v>NEE</v>
+        <v>LEVI</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1032,7 +1026,7 @@
       </c>
       <c r="B14" t="str">
         <f>VLOOKUP(A14,[1]Sheet1!$C:$C,1,0)</f>
-        <v>C</v>
+        <v>WMT</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1041,7 +1035,7 @@
       </c>
       <c r="B15" t="str">
         <f>VLOOKUP(A15,[1]Sheet1!$C:$C,1,0)</f>
-        <v>AVGO</v>
+        <v>TSM</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -1050,7 +1044,7 @@
       </c>
       <c r="B16" t="str">
         <f>VLOOKUP(A16,[1]Sheet1!$C:$C,1,0)</f>
-        <v>MC.PA</v>
+        <v>AMAT</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -1059,7 +1053,7 @@
       </c>
       <c r="B17" t="str">
         <f>VLOOKUP(A17,[1]Sheet1!$C:$C,1,0)</f>
-        <v>TSM</v>
+        <v>US30</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1068,7 +1062,7 @@
       </c>
       <c r="B18" t="str">
         <f>VLOOKUP(A18,[1]Sheet1!$C:$C,1,0)</f>
-        <v>MA</v>
+        <v>BBVA.MC</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -1077,7 +1071,7 @@
       </c>
       <c r="B19" t="str">
         <f>VLOOKUP(A19,[1]Sheet1!$C:$C,1,0)</f>
-        <v>MAXN</v>
+        <v>SDIA.L</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -1086,7 +1080,7 @@
       </c>
       <c r="B20" t="str">
         <f>VLOOKUP(A20,[1]Sheet1!$C:$C,1,0)</f>
-        <v>SQM</v>
+        <v>SPY</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -1095,7 +1089,7 @@
       </c>
       <c r="B21" t="str">
         <f>VLOOKUP(A21,[1]Sheet1!$C:$C,1,0)</f>
-        <v>ASML</v>
+        <v>SHELL.AS</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -1104,7 +1098,7 @@
       </c>
       <c r="B22" t="str">
         <f>VLOOKUP(A22,[1]Sheet1!$C:$C,1,0)</f>
-        <v>MO</v>
+        <v>DUK</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -1113,7 +1107,7 @@
       </c>
       <c r="B23" t="str">
         <f>VLOOKUP(A23,[1]Sheet1!$C:$C,1,0)</f>
-        <v>MXN=X</v>
+        <v>QCOM</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -1122,7 +1116,7 @@
       </c>
       <c r="B24" t="str">
         <f>VLOOKUP(A24,[1]Sheet1!$C:$C,1,0)</f>
-        <v>INGR</v>
+        <v>FSLR</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -1131,7 +1125,7 @@
       </c>
       <c r="B25" t="str">
         <f>VLOOKUP(A25,[1]Sheet1!$C:$C,1,0)</f>
-        <v>BAP</v>
+        <v>GILD</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -1140,7 +1134,7 @@
       </c>
       <c r="B26" t="str">
         <f>VLOOKUP(A26,[1]Sheet1!$C:$C,1,0)</f>
-        <v>DUK</v>
+        <v>AVGO</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -1158,7 +1152,7 @@
       </c>
       <c r="B28" t="str">
         <f>VLOOKUP(A28,[1]Sheet1!$C:$C,1,0)</f>
-        <v>^VIX</v>
+        <v>YUM</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -1167,7 +1161,7 @@
       </c>
       <c r="B29" t="str">
         <f>VLOOKUP(A29,[1]Sheet1!$C:$C,1,0)</f>
-        <v>AEP</v>
+        <v>V</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -1176,7 +1170,7 @@
       </c>
       <c r="B30" t="str">
         <f>VLOOKUP(A30,[1]Sheet1!$C:$C,1,0)</f>
-        <v>AMAT</v>
+        <v>INGR</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -1185,7 +1179,7 @@
       </c>
       <c r="B31" t="str">
         <f>VLOOKUP(A31,[1]Sheet1!$C:$C,1,0)</f>
-        <v>YUM</v>
+        <v>CIB</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -1194,7 +1188,7 @@
       </c>
       <c r="B32" t="str">
         <f>VLOOKUP(A32,[1]Sheet1!$C:$C,1,0)</f>
-        <v>VHYD.L</v>
+        <v>GOOGL</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -1203,7 +1197,7 @@
       </c>
       <c r="B33" t="str">
         <f>VLOOKUP(A33,[1]Sheet1!$C:$C,1,0)</f>
-        <v>PANW</v>
+        <v>ING</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -1212,7 +1206,7 @@
       </c>
       <c r="B34" t="str">
         <f>VLOOKUP(A34,[1]Sheet1!$C:$C,1,0)</f>
-        <v>JPY=X</v>
+        <v>ACI</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -1221,7 +1215,7 @@
       </c>
       <c r="B35" t="str">
         <f>VLOOKUP(A35,[1]Sheet1!$C:$C,1,0)</f>
-        <v>BND</v>
+        <v>MC.PA</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -1230,7 +1224,7 @@
       </c>
       <c r="B36" t="str">
         <f>VLOOKUP(A36,[1]Sheet1!$C:$C,1,0)</f>
-        <v>SHELL.AS</v>
+        <v>AEP</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -1239,7 +1233,7 @@
       </c>
       <c r="B37" t="str">
         <f>VLOOKUP(A37,[1]Sheet1!$C:$C,1,0)</f>
-        <v>DAR</v>
+        <v>PANW</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -1248,7 +1242,7 @@
       </c>
       <c r="B38" t="str">
         <f>VLOOKUP(A38,[1]Sheet1!$C:$C,1,0)</f>
-        <v>CIB</v>
+        <v>^VIX</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -1257,7 +1251,7 @@
       </c>
       <c r="B39" t="str">
         <f>VLOOKUP(A39,[1]Sheet1!$C:$C,1,0)</f>
-        <v>EXC</v>
+        <v>PEP</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -1266,7 +1260,7 @@
       </c>
       <c r="B40" t="str">
         <f>VLOOKUP(A40,[1]Sheet1!$C:$C,1,0)</f>
-        <v>SMFG</v>
+        <v>BAP</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -1275,7 +1269,7 @@
       </c>
       <c r="B41" t="str">
         <f>VLOOKUP(A41,[1]Sheet1!$C:$C,1,0)</f>
-        <v>GILD</v>
+        <v>YPF</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -1284,7 +1278,7 @@
       </c>
       <c r="B42" t="str">
         <f>VLOOKUP(A42,[1]Sheet1!$C:$C,1,0)</f>
-        <v>PEP</v>
+        <v>VBTC.DE</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -1293,7 +1287,7 @@
       </c>
       <c r="B43" t="str">
         <f>VLOOKUP(A43,[1]Sheet1!$C:$C,1,0)</f>
-        <v>KMB</v>
+        <v>SMFG</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -1302,7 +1296,7 @@
       </c>
       <c r="B44" t="str">
         <f>VLOOKUP(A44,[1]Sheet1!$C:$C,1,0)</f>
-        <v>GC=F</v>
+        <v>AAPL</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -1311,7 +1305,7 @@
       </c>
       <c r="B45" t="str">
         <f>VLOOKUP(A45,[1]Sheet1!$C:$C,1,0)</f>
-        <v>BBVA.MC</v>
+        <v>C</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -1320,7 +1314,7 @@
       </c>
       <c r="B46" t="str">
         <f>VLOOKUP(A46,[1]Sheet1!$C:$C,1,0)</f>
-        <v>VBTC.DE</v>
+        <v>GC=F</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -1329,7 +1323,7 @@
       </c>
       <c r="B47" t="str">
         <f>VLOOKUP(A47,[1]Sheet1!$C:$C,1,0)</f>
-        <v>GOOGL</v>
+        <v>AGIO</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -1338,7 +1332,7 @@
       </c>
       <c r="B48" t="str">
         <f>VLOOKUP(A48,[1]Sheet1!$C:$C,1,0)</f>
-        <v>APA</v>
+        <v>MSFT</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -1347,7 +1341,7 @@
       </c>
       <c r="B49" t="str">
         <f>VLOOKUP(A49,[1]Sheet1!$C:$C,1,0)</f>
-        <v>MSFT</v>
+        <v>MXN=X</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -1356,7 +1350,7 @@
       </c>
       <c r="B50" t="str">
         <f>VLOOKUP(A50,[1]Sheet1!$C:$C,1,0)</f>
-        <v>SPY</v>
+        <v>NEE</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -1365,7 +1359,7 @@
       </c>
       <c r="B51" t="str">
         <f>VLOOKUP(A51,[1]Sheet1!$C:$C,1,0)</f>
-        <v>V</v>
+        <v>SQM</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -1374,7 +1368,7 @@
       </c>
       <c r="B52" t="str">
         <f>VLOOKUP(A52,[1]Sheet1!$C:$C,1,0)</f>
-        <v>BOTZ.L</v>
+        <v>BATT.AS</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -1383,7 +1377,7 @@
       </c>
       <c r="B53" t="str">
         <f>VLOOKUP(A53,[1]Sheet1!$C:$C,1,0)</f>
-        <v>QCOM</v>
+        <v>MAXN</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -1392,7 +1386,7 @@
       </c>
       <c r="B54" t="str">
         <f>VLOOKUP(A54,[1]Sheet1!$C:$C,1,0)</f>
-        <v>VWO</v>
+        <v>EXC</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -1401,7 +1395,7 @@
       </c>
       <c r="B55" t="str">
         <f>VLOOKUP(A55,[1]Sheet1!$C:$C,1,0)</f>
-        <v>YPF</v>
+        <v>MO</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -1410,7 +1404,7 @@
       </c>
       <c r="B56" t="str">
         <f>VLOOKUP(A56,[1]Sheet1!$C:$C,1,0)</f>
-        <v>ING</v>
+        <v>APA</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -1419,7 +1413,7 @@
       </c>
       <c r="B57" t="str">
         <f>VLOOKUP(A57,[1]Sheet1!$C:$C,1,0)</f>
-        <v>AAPL</v>
+        <v>ASML</v>
       </c>
     </row>
   </sheetData>

--- a/Stock Selection/tickers_update.xlsx
+++ b/Stock Selection/tickers_update.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rodwals-my.sharepoint.com/personal/samuel_rodwal_com/Documents/Professional_WorkTools/Github/RodWal-Capital-Insights/Stock Selection/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_08B59E045E5BCA0E62355476589BBE7AA63F8035" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8E1F2D1-F234-45E0-875F-C861A34BB043}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_08B5094C5858DC0E6235547658229EB9844780B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED15DBA4-0033-4EC8-A7E4-A574AF37879C}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="615" windowWidth="13920" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4575" yWindow="1245" windowWidth="19155" windowHeight="13725" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,9 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$59</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,174 +39,180 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>Ticker</t>
   </si>
   <si>
+    <t>AEP</t>
+  </si>
+  <si>
+    <t>YUM</t>
+  </si>
+  <si>
+    <t>SDIA.L</t>
+  </si>
+  <si>
+    <t>DUK</t>
+  </si>
+  <si>
+    <t>CIB</t>
+  </si>
+  <si>
+    <t>AVGO</t>
+  </si>
+  <si>
+    <t>AGIO</t>
+  </si>
+  <si>
+    <t>NEE</t>
+  </si>
+  <si>
+    <t>MAXN</t>
+  </si>
+  <si>
+    <t>COIN</t>
+  </si>
+  <si>
+    <t>BBVA.MC</t>
+  </si>
+  <si>
+    <t>BCS</t>
+  </si>
+  <si>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>ASML</t>
+  </si>
+  <si>
+    <t>GC=F</t>
+  </si>
+  <si>
+    <t>MXN=X</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>APA</t>
+  </si>
+  <si>
+    <t>QCOM</t>
+  </si>
+  <si>
+    <t>YPF</t>
+  </si>
+  <si>
+    <t>GOOGL</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>^VIX</t>
+  </si>
+  <si>
+    <t>GIS</t>
+  </si>
+  <si>
+    <t>WMT</t>
+  </si>
+  <si>
+    <t>GILD</t>
+  </si>
+  <si>
+    <t>US30</t>
+  </si>
+  <si>
+    <t>SHELL.AS</t>
+  </si>
+  <si>
+    <t>JPY=X</t>
+  </si>
+  <si>
+    <t>MSFT</t>
+  </si>
+  <si>
+    <t>MC.PA</t>
+  </si>
+  <si>
+    <t>VWO</t>
+  </si>
+  <si>
+    <t>ACI</t>
+  </si>
+  <si>
+    <t>AMAT</t>
+  </si>
+  <si>
+    <t>KMB</t>
+  </si>
+  <si>
+    <t>BATT.AS</t>
+  </si>
+  <si>
+    <t>VHYD.L</t>
+  </si>
+  <si>
+    <t>EXC</t>
+  </si>
+  <si>
+    <t>LEVI</t>
+  </si>
+  <si>
+    <t>SPY</t>
+  </si>
+  <si>
+    <t>ING</t>
+  </si>
+  <si>
+    <t>PEP</t>
+  </si>
+  <si>
+    <t>BOTZ.L</t>
+  </si>
+  <si>
+    <t>SQM</t>
+  </si>
+  <si>
+    <t>AAPL</t>
+  </si>
+  <si>
+    <t>PANW</t>
+  </si>
+  <si>
+    <t>INGR</t>
+  </si>
+  <si>
+    <t>TSM</t>
+  </si>
+  <si>
+    <t>VBTC.DE</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>FLOA.L</t>
+  </si>
+  <si>
+    <t>SMFG</t>
+  </si>
+  <si>
+    <t>BAP</t>
+  </si>
+  <si>
+    <t>FSLR</t>
+  </si>
+  <si>
+    <t>DAR</t>
+  </si>
+  <si>
     <t>BND</t>
   </si>
   <si>
-    <t>BOTZ.L</t>
-  </si>
-  <si>
-    <t>JPY=X</t>
-  </si>
-  <si>
-    <t>FLOA.L</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>VWO</t>
-  </si>
-  <si>
-    <t>KMB</t>
-  </si>
-  <si>
-    <t>BCS</t>
-  </si>
-  <si>
-    <t>DAR</t>
-  </si>
-  <si>
-    <t>VHYD.L</t>
-  </si>
-  <si>
-    <t>LEVI</t>
-  </si>
-  <si>
-    <t>WMT</t>
-  </si>
-  <si>
-    <t>TSM</t>
-  </si>
-  <si>
-    <t>AMAT</t>
-  </si>
-  <si>
-    <t>US30</t>
-  </si>
-  <si>
-    <t>BBVA.MC</t>
-  </si>
-  <si>
-    <t>SDIA.L</t>
-  </si>
-  <si>
-    <t>SPY</t>
-  </si>
-  <si>
-    <t>SHELL.AS</t>
-  </si>
-  <si>
-    <t>DUK</t>
-  </si>
-  <si>
-    <t>QCOM</t>
-  </si>
-  <si>
-    <t>FSLR</t>
-  </si>
-  <si>
-    <t>GILD</t>
-  </si>
-  <si>
-    <t>AVGO</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>YUM</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>INGR</t>
-  </si>
-  <si>
-    <t>CIB</t>
-  </si>
-  <si>
-    <t>GOOGL</t>
-  </si>
-  <si>
-    <t>ING</t>
-  </si>
-  <si>
-    <t>ACI</t>
-  </si>
-  <si>
-    <t>MC.PA</t>
-  </si>
-  <si>
-    <t>AEP</t>
-  </si>
-  <si>
-    <t>PANW</t>
-  </si>
-  <si>
-    <t>^VIX</t>
-  </si>
-  <si>
-    <t>PEP</t>
-  </si>
-  <si>
-    <t>BAP</t>
-  </si>
-  <si>
-    <t>YPF</t>
-  </si>
-  <si>
-    <t>VBTC.DE</t>
-  </si>
-  <si>
-    <t>SMFG</t>
-  </si>
-  <si>
-    <t>AAPL</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>GC=F</t>
-  </si>
-  <si>
-    <t>AGIO</t>
-  </si>
-  <si>
-    <t>MSFT</t>
-  </si>
-  <si>
-    <t>MXN=X</t>
-  </si>
-  <si>
-    <t>NEE</t>
-  </si>
-  <si>
-    <t>SQM</t>
-  </si>
-  <si>
-    <t>BATT.AS</t>
-  </si>
-  <si>
-    <t>MAXN</t>
-  </si>
-  <si>
-    <t>EXC</t>
-  </si>
-  <si>
     <t>MO</t>
-  </si>
-  <si>
-    <t>APA</t>
-  </si>
-  <si>
-    <t>ASML</t>
   </si>
 </sst>
 </file>
@@ -620,6 +629,16 @@
         <row r="67">
           <cell r="C67" t="str">
             <v>BAP</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="C68" t="str">
+            <v>COIN</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="C69" t="str">
+            <v>GIS</v>
           </cell>
         </row>
       </sheetData>
@@ -913,7 +932,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B57"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -921,211 +941,212 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="str">
         <f>VLOOKUP(A2,[1]Sheet1!$C:$C,1,0)</f>
-        <v>BND</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>AEP</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3" t="str">
         <f>VLOOKUP(A3,[1]Sheet1!$C:$C,1,0)</f>
-        <v>BOTZ.L</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>YUM</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="str">
         <f>VLOOKUP(A4,[1]Sheet1!$C:$C,1,0)</f>
-        <v>JPY=X</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>SDIA.L</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5" t="str">
         <f>VLOOKUP(A5,[1]Sheet1!$C:$C,1,0)</f>
-        <v>FLOA.L</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>DUK</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6" t="str">
         <f>VLOOKUP(A6,[1]Sheet1!$C:$C,1,0)</f>
-        <v>MA</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>CIB</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7" t="str">
         <f>VLOOKUP(A7,[1]Sheet1!$C:$C,1,0)</f>
-        <v>VWO</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>AVGO</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8" t="str">
         <f>VLOOKUP(A8,[1]Sheet1!$C:$C,1,0)</f>
-        <v>KMB</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+        <v>AGIO</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>8</v>
-      </c>
-      <c r="B9" t="str">
-        <f>VLOOKUP(A9,[1]Sheet1!$C:$C,1,0)</f>
-        <v>BCS</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>9</v>
       </c>
       <c r="B10" t="str">
         <f>VLOOKUP(A10,[1]Sheet1!$C:$C,1,0)</f>
-        <v>DAR</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>NEE</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" t="str">
         <f>VLOOKUP(A11,[1]Sheet1!$C:$C,1,0)</f>
-        <v>VHYD.L</v>
+        <v>MAXN</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" t="str">
         <f>VLOOKUP(A12,[1]Sheet1!$C:$C,1,0)</f>
-        <v>LEVI</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>COIN</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" t="str">
+        <f>VLOOKUP(A13,[1]Sheet1!$C:$C,1,0)</f>
+        <v>BBVA.MC</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
       <c r="B14" t="str">
         <f>VLOOKUP(A14,[1]Sheet1!$C:$C,1,0)</f>
-        <v>WMT</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>BCS</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
       <c r="B15" t="str">
         <f>VLOOKUP(A15,[1]Sheet1!$C:$C,1,0)</f>
-        <v>TSM</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>MA</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
       <c r="B16" t="str">
         <f>VLOOKUP(A16,[1]Sheet1!$C:$C,1,0)</f>
-        <v>AMAT</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <v>ASML</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>15</v>
       </c>
       <c r="B17" t="str">
         <f>VLOOKUP(A17,[1]Sheet1!$C:$C,1,0)</f>
-        <v>US30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>GC=F</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>16</v>
       </c>
       <c r="B18" t="str">
         <f>VLOOKUP(A18,[1]Sheet1!$C:$C,1,0)</f>
-        <v>BBVA.MC</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>MXN=X</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>17</v>
       </c>
       <c r="B19" t="str">
         <f>VLOOKUP(A19,[1]Sheet1!$C:$C,1,0)</f>
-        <v>SDIA.L</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>NVDA</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>18</v>
       </c>
       <c r="B20" t="str">
         <f>VLOOKUP(A20,[1]Sheet1!$C:$C,1,0)</f>
-        <v>SPY</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+        <v>APA</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>19</v>
       </c>
       <c r="B21" t="str">
         <f>VLOOKUP(A21,[1]Sheet1!$C:$C,1,0)</f>
-        <v>SHELL.AS</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+        <v>QCOM</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>20</v>
       </c>
       <c r="B22" t="str">
         <f>VLOOKUP(A22,[1]Sheet1!$C:$C,1,0)</f>
-        <v>DUK</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+        <v>YPF</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>21</v>
       </c>
       <c r="B23" t="str">
         <f>VLOOKUP(A23,[1]Sheet1!$C:$C,1,0)</f>
-        <v>QCOM</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+        <v>GOOGL</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>22</v>
       </c>
       <c r="B24" t="str">
         <f>VLOOKUP(A24,[1]Sheet1!$C:$C,1,0)</f>
-        <v>FSLR</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+        <v>V</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>23</v>
       </c>
       <c r="B25" t="str">
         <f>VLOOKUP(A25,[1]Sheet1!$C:$C,1,0)</f>
-        <v>GILD</v>
+        <v>^VIX</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -1134,289 +1155,314 @@
       </c>
       <c r="B26" t="str">
         <f>VLOOKUP(A26,[1]Sheet1!$C:$C,1,0)</f>
-        <v>AVGO</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+        <v>GIS</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>25</v>
       </c>
       <c r="B27" t="str">
         <f>VLOOKUP(A27,[1]Sheet1!$C:$C,1,0)</f>
-        <v>NVDA</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+        <v>WMT</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>26</v>
       </c>
       <c r="B28" t="str">
         <f>VLOOKUP(A28,[1]Sheet1!$C:$C,1,0)</f>
-        <v>YUM</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+        <v>GILD</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>27</v>
       </c>
       <c r="B29" t="str">
         <f>VLOOKUP(A29,[1]Sheet1!$C:$C,1,0)</f>
-        <v>V</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+        <v>US30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>28</v>
       </c>
       <c r="B30" t="str">
         <f>VLOOKUP(A30,[1]Sheet1!$C:$C,1,0)</f>
-        <v>INGR</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+        <v>SHELL.AS</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>29</v>
       </c>
       <c r="B31" t="str">
         <f>VLOOKUP(A31,[1]Sheet1!$C:$C,1,0)</f>
-        <v>CIB</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+        <v>JPY=X</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>30</v>
       </c>
       <c r="B32" t="str">
         <f>VLOOKUP(A32,[1]Sheet1!$C:$C,1,0)</f>
-        <v>GOOGL</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+        <v>MSFT</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>31</v>
       </c>
       <c r="B33" t="str">
         <f>VLOOKUP(A33,[1]Sheet1!$C:$C,1,0)</f>
-        <v>ING</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+        <v>MC.PA</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>32</v>
       </c>
       <c r="B34" t="str">
         <f>VLOOKUP(A34,[1]Sheet1!$C:$C,1,0)</f>
-        <v>ACI</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+        <v>VWO</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>33</v>
       </c>
       <c r="B35" t="str">
         <f>VLOOKUP(A35,[1]Sheet1!$C:$C,1,0)</f>
-        <v>MC.PA</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+        <v>ACI</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>34</v>
       </c>
       <c r="B36" t="str">
         <f>VLOOKUP(A36,[1]Sheet1!$C:$C,1,0)</f>
-        <v>AEP</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+        <v>AMAT</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>35</v>
       </c>
       <c r="B37" t="str">
         <f>VLOOKUP(A37,[1]Sheet1!$C:$C,1,0)</f>
-        <v>PANW</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+        <v>KMB</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>36</v>
       </c>
       <c r="B38" t="str">
         <f>VLOOKUP(A38,[1]Sheet1!$C:$C,1,0)</f>
-        <v>^VIX</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+        <v>BATT.AS</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>37</v>
       </c>
       <c r="B39" t="str">
         <f>VLOOKUP(A39,[1]Sheet1!$C:$C,1,0)</f>
-        <v>PEP</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+        <v>VHYD.L</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>38</v>
       </c>
       <c r="B40" t="str">
         <f>VLOOKUP(A40,[1]Sheet1!$C:$C,1,0)</f>
-        <v>BAP</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+        <v>EXC</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>39</v>
       </c>
       <c r="B41" t="str">
         <f>VLOOKUP(A41,[1]Sheet1!$C:$C,1,0)</f>
-        <v>YPF</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+        <v>LEVI</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>40</v>
       </c>
       <c r="B42" t="str">
         <f>VLOOKUP(A42,[1]Sheet1!$C:$C,1,0)</f>
-        <v>VBTC.DE</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+        <v>SPY</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>41</v>
       </c>
       <c r="B43" t="str">
         <f>VLOOKUP(A43,[1]Sheet1!$C:$C,1,0)</f>
-        <v>SMFG</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+        <v>ING</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>42</v>
       </c>
       <c r="B44" t="str">
         <f>VLOOKUP(A44,[1]Sheet1!$C:$C,1,0)</f>
-        <v>AAPL</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+        <v>PEP</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>43</v>
       </c>
       <c r="B45" t="str">
         <f>VLOOKUP(A45,[1]Sheet1!$C:$C,1,0)</f>
-        <v>C</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+        <v>BOTZ.L</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>44</v>
       </c>
       <c r="B46" t="str">
         <f>VLOOKUP(A46,[1]Sheet1!$C:$C,1,0)</f>
-        <v>GC=F</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+        <v>SQM</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>45</v>
       </c>
       <c r="B47" t="str">
         <f>VLOOKUP(A47,[1]Sheet1!$C:$C,1,0)</f>
-        <v>AGIO</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+        <v>AAPL</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>46</v>
       </c>
       <c r="B48" t="str">
         <f>VLOOKUP(A48,[1]Sheet1!$C:$C,1,0)</f>
-        <v>MSFT</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+        <v>PANW</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>47</v>
       </c>
       <c r="B49" t="str">
         <f>VLOOKUP(A49,[1]Sheet1!$C:$C,1,0)</f>
-        <v>MXN=X</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+        <v>INGR</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>48</v>
       </c>
       <c r="B50" t="str">
         <f>VLOOKUP(A50,[1]Sheet1!$C:$C,1,0)</f>
-        <v>NEE</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+        <v>TSM</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>49</v>
       </c>
       <c r="B51" t="str">
         <f>VLOOKUP(A51,[1]Sheet1!$C:$C,1,0)</f>
-        <v>SQM</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+        <v>VBTC.DE</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>50</v>
       </c>
       <c r="B52" t="str">
         <f>VLOOKUP(A52,[1]Sheet1!$C:$C,1,0)</f>
-        <v>BATT.AS</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>51</v>
       </c>
       <c r="B53" t="str">
         <f>VLOOKUP(A53,[1]Sheet1!$C:$C,1,0)</f>
-        <v>MAXN</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+        <v>FLOA.L</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>52</v>
       </c>
       <c r="B54" t="str">
         <f>VLOOKUP(A54,[1]Sheet1!$C:$C,1,0)</f>
-        <v>EXC</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+        <v>SMFG</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>53</v>
       </c>
       <c r="B55" t="str">
         <f>VLOOKUP(A55,[1]Sheet1!$C:$C,1,0)</f>
-        <v>MO</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+        <v>BAP</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>54</v>
       </c>
       <c r="B56" t="str">
         <f>VLOOKUP(A56,[1]Sheet1!$C:$C,1,0)</f>
-        <v>APA</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+        <v>FSLR</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>55</v>
       </c>
       <c r="B57" t="str">
         <f>VLOOKUP(A57,[1]Sheet1!$C:$C,1,0)</f>
-        <v>ASML</v>
+        <v>DAR</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>56</v>
+      </c>
+      <c r="B58" t="str">
+        <f>VLOOKUP(A58,[1]Sheet1!$C:$C,1,0)</f>
+        <v>BND</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>57</v>
+      </c>
+      <c r="B59" t="str">
+        <f>VLOOKUP(A59,[1]Sheet1!$C:$C,1,0)</f>
+        <v>MO</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B59" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="#N/A"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Stock Selection/tickers_update.xlsx
+++ b/Stock Selection/tickers_update.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rodwals-my.sharepoint.com/personal/samuel_rodwal_com/Documents/Professional_WorkTools/Github/RodWal-Capital-Insights/Stock Selection/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_08B5094C5858DC0E6235547658229EB9844780B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED15DBA4-0033-4EC8-A7E4-A574AF37879C}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_08B5C83C9A69360E6235547658BCDEFAA871838A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CEAEB528-0177-4259-A35A-4F9AD5960B17}"/>
   <bookViews>
-    <workbookView xWindow="4575" yWindow="1245" windowWidth="19155" windowHeight="13725" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,6 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$59</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -39,180 +36,204 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>Ticker</t>
   </si>
   <si>
+    <t>DAR</t>
+  </si>
+  <si>
+    <t>US30</t>
+  </si>
+  <si>
+    <t>APA</t>
+  </si>
+  <si>
+    <t>TTE</t>
+  </si>
+  <si>
+    <t>GC=F</t>
+  </si>
+  <si>
+    <t>EXC</t>
+  </si>
+  <si>
+    <t>AMAT</t>
+  </si>
+  <si>
+    <t>MXN=X</t>
+  </si>
+  <si>
+    <t>GIS</t>
+  </si>
+  <si>
+    <t>ASML</t>
+  </si>
+  <si>
+    <t>ACI</t>
+  </si>
+  <si>
+    <t>YUM</t>
+  </si>
+  <si>
+    <t>MSFT</t>
+  </si>
+  <si>
+    <t>GOOGL</t>
+  </si>
+  <si>
+    <t>BBVA</t>
+  </si>
+  <si>
+    <t>BAP</t>
+  </si>
+  <si>
+    <t>PANW</t>
+  </si>
+  <si>
+    <t>AGIO</t>
+  </si>
+  <si>
+    <t>BTCE.DE</t>
+  </si>
+  <si>
+    <t>MC.PA</t>
+  </si>
+  <si>
+    <t>ING</t>
+  </si>
+  <si>
+    <t>BBAR</t>
+  </si>
+  <si>
+    <t>BBVA.MC</t>
+  </si>
+  <si>
+    <t>BOTZ.L</t>
+  </si>
+  <si>
+    <t>YPF</t>
+  </si>
+  <si>
+    <t>TSM</t>
+  </si>
+  <si>
+    <t>PEP</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
+    <t>EQNR</t>
+  </si>
+  <si>
     <t>AEP</t>
   </si>
   <si>
-    <t>YUM</t>
+    <t>SMFG</t>
+  </si>
+  <si>
+    <t>AAPL</t>
+  </si>
+  <si>
+    <t>VBTC.DE</t>
+  </si>
+  <si>
+    <t>BATT.AS</t>
+  </si>
+  <si>
+    <t>SQM</t>
+  </si>
+  <si>
+    <t>NEE</t>
+  </si>
+  <si>
+    <t>LEVI</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>CIB</t>
+  </si>
+  <si>
+    <t>SPY</t>
+  </si>
+  <si>
+    <t>AVGO</t>
+  </si>
+  <si>
+    <t>COIN</t>
+  </si>
+  <si>
+    <t>FLOA.L</t>
+  </si>
+  <si>
+    <t>KMB</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>JPY=X</t>
+  </si>
+  <si>
+    <t>FSLR</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>VHYD.L</t>
+  </si>
+  <si>
+    <t>JKS</t>
+  </si>
+  <si>
+    <t>SHELL.AS</t>
+  </si>
+  <si>
+    <t>WMT</t>
+  </si>
+  <si>
+    <t>BCS</t>
+  </si>
+  <si>
+    <t>QCOM</t>
+  </si>
+  <si>
+    <t>MAXN</t>
+  </si>
+  <si>
+    <t>INGR</t>
+  </si>
+  <si>
+    <t>MO</t>
+  </si>
+  <si>
+    <t>GILD</t>
+  </si>
+  <si>
+    <t>DUK</t>
+  </si>
+  <si>
+    <t>^VIX</t>
+  </si>
+  <si>
+    <t>BND</t>
+  </si>
+  <si>
+    <t>VWO</t>
+  </si>
+  <si>
+    <t>PHGP.L</t>
   </si>
   <si>
     <t>SDIA.L</t>
-  </si>
-  <si>
-    <t>DUK</t>
-  </si>
-  <si>
-    <t>CIB</t>
-  </si>
-  <si>
-    <t>AVGO</t>
-  </si>
-  <si>
-    <t>AGIO</t>
-  </si>
-  <si>
-    <t>NEE</t>
-  </si>
-  <si>
-    <t>MAXN</t>
-  </si>
-  <si>
-    <t>COIN</t>
-  </si>
-  <si>
-    <t>BBVA.MC</t>
-  </si>
-  <si>
-    <t>BCS</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>ASML</t>
-  </si>
-  <si>
-    <t>GC=F</t>
-  </si>
-  <si>
-    <t>MXN=X</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>APA</t>
-  </si>
-  <si>
-    <t>QCOM</t>
-  </si>
-  <si>
-    <t>YPF</t>
-  </si>
-  <si>
-    <t>GOOGL</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>^VIX</t>
-  </si>
-  <si>
-    <t>GIS</t>
-  </si>
-  <si>
-    <t>WMT</t>
-  </si>
-  <si>
-    <t>GILD</t>
-  </si>
-  <si>
-    <t>US30</t>
-  </si>
-  <si>
-    <t>SHELL.AS</t>
-  </si>
-  <si>
-    <t>JPY=X</t>
-  </si>
-  <si>
-    <t>MSFT</t>
-  </si>
-  <si>
-    <t>MC.PA</t>
-  </si>
-  <si>
-    <t>VWO</t>
-  </si>
-  <si>
-    <t>ACI</t>
-  </si>
-  <si>
-    <t>AMAT</t>
-  </si>
-  <si>
-    <t>KMB</t>
-  </si>
-  <si>
-    <t>BATT.AS</t>
-  </si>
-  <si>
-    <t>VHYD.L</t>
-  </si>
-  <si>
-    <t>EXC</t>
-  </si>
-  <si>
-    <t>LEVI</t>
-  </si>
-  <si>
-    <t>SPY</t>
-  </si>
-  <si>
-    <t>ING</t>
-  </si>
-  <si>
-    <t>PEP</t>
-  </si>
-  <si>
-    <t>BOTZ.L</t>
-  </si>
-  <si>
-    <t>SQM</t>
-  </si>
-  <si>
-    <t>AAPL</t>
-  </si>
-  <si>
-    <t>PANW</t>
-  </si>
-  <si>
-    <t>INGR</t>
-  </si>
-  <si>
-    <t>TSM</t>
-  </si>
-  <si>
-    <t>VBTC.DE</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>FLOA.L</t>
-  </si>
-  <si>
-    <t>SMFG</t>
-  </si>
-  <si>
-    <t>BAP</t>
-  </si>
-  <si>
-    <t>FSLR</t>
-  </si>
-  <si>
-    <t>DAR</t>
-  </si>
-  <si>
-    <t>BND</t>
-  </si>
-  <si>
-    <t>MO</t>
   </si>
 </sst>
 </file>
@@ -231,6 +252,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -639,6 +661,41 @@
         <row r="69">
           <cell r="C69" t="str">
             <v>GIS</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="C70" t="str">
+            <v>SLV</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="C71" t="str">
+            <v>BBVA</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="C72" t="str">
+            <v>BBAR</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="C73" t="str">
+            <v>BTCE.DE</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="C74" t="str">
+            <v>TTE</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="C75" t="str">
+            <v>EQNR</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="C76" t="str">
+            <v>PHGP.L</v>
           </cell>
         </row>
       </sheetData>
@@ -932,8 +989,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:B59"/>
+  <dimension ref="A1:B66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -941,528 +997,592 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="str">
         <f>VLOOKUP(A2,[1]Sheet1!$C:$C,1,0)</f>
-        <v>AEP</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>DAR</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3" t="str">
         <f>VLOOKUP(A3,[1]Sheet1!$C:$C,1,0)</f>
-        <v>YUM</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>US30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="str">
         <f>VLOOKUP(A4,[1]Sheet1!$C:$C,1,0)</f>
-        <v>SDIA.L</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>APA</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5" t="str">
         <f>VLOOKUP(A5,[1]Sheet1!$C:$C,1,0)</f>
-        <v>DUK</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>TTE</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6" t="str">
         <f>VLOOKUP(A6,[1]Sheet1!$C:$C,1,0)</f>
-        <v>CIB</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>GC=F</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7" t="str">
         <f>VLOOKUP(A7,[1]Sheet1!$C:$C,1,0)</f>
-        <v>AVGO</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>EXC</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8" t="str">
         <f>VLOOKUP(A8,[1]Sheet1!$C:$C,1,0)</f>
-        <v>AGIO</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>AMAT</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str">
+        <f>VLOOKUP(A9,[1]Sheet1!$C:$C,1,0)</f>
+        <v>MXN=X</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" t="str">
         <f>VLOOKUP(A10,[1]Sheet1!$C:$C,1,0)</f>
-        <v>NEE</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>GIS</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" t="str">
         <f>VLOOKUP(A11,[1]Sheet1!$C:$C,1,0)</f>
-        <v>MAXN</v>
+        <v>ASML</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" t="str">
         <f>VLOOKUP(A12,[1]Sheet1!$C:$C,1,0)</f>
-        <v>COIN</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>ACI</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" t="str">
         <f>VLOOKUP(A13,[1]Sheet1!$C:$C,1,0)</f>
-        <v>BBVA.MC</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>YUM</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="str">
         <f>VLOOKUP(A14,[1]Sheet1!$C:$C,1,0)</f>
-        <v>BCS</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>MSFT</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" t="str">
         <f>VLOOKUP(A15,[1]Sheet1!$C:$C,1,0)</f>
-        <v>MA</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>GOOGL</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" t="str">
         <f>VLOOKUP(A16,[1]Sheet1!$C:$C,1,0)</f>
-        <v>ASML</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>BBVA</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" t="str">
         <f>VLOOKUP(A17,[1]Sheet1!$C:$C,1,0)</f>
-        <v>GC=F</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>BAP</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" t="str">
         <f>VLOOKUP(A18,[1]Sheet1!$C:$C,1,0)</f>
-        <v>MXN=X</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>PANW</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" t="str">
         <f>VLOOKUP(A19,[1]Sheet1!$C:$C,1,0)</f>
-        <v>NVDA</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>AGIO</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" t="str">
         <f>VLOOKUP(A20,[1]Sheet1!$C:$C,1,0)</f>
-        <v>APA</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>BTCE.DE</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" t="str">
         <f>VLOOKUP(A21,[1]Sheet1!$C:$C,1,0)</f>
-        <v>QCOM</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>MC.PA</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" t="str">
         <f>VLOOKUP(A22,[1]Sheet1!$C:$C,1,0)</f>
-        <v>YPF</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>ING</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" t="str">
         <f>VLOOKUP(A23,[1]Sheet1!$C:$C,1,0)</f>
-        <v>GOOGL</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>BBAR</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" t="str">
         <f>VLOOKUP(A24,[1]Sheet1!$C:$C,1,0)</f>
-        <v>V</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>BBVA.MC</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" t="str">
         <f>VLOOKUP(A25,[1]Sheet1!$C:$C,1,0)</f>
-        <v>^VIX</v>
+        <v>BOTZ.L</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" t="str">
         <f>VLOOKUP(A26,[1]Sheet1!$C:$C,1,0)</f>
-        <v>GIS</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>YPF</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" t="str">
         <f>VLOOKUP(A27,[1]Sheet1!$C:$C,1,0)</f>
-        <v>WMT</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>TSM</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" t="str">
         <f>VLOOKUP(A28,[1]Sheet1!$C:$C,1,0)</f>
-        <v>GILD</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>PEP</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" t="str">
         <f>VLOOKUP(A29,[1]Sheet1!$C:$C,1,0)</f>
-        <v>US30</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>SLV</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" t="str">
         <f>VLOOKUP(A30,[1]Sheet1!$C:$C,1,0)</f>
-        <v>SHELL.AS</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>EQNR</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" t="str">
         <f>VLOOKUP(A31,[1]Sheet1!$C:$C,1,0)</f>
-        <v>JPY=X</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>AEP</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" t="str">
         <f>VLOOKUP(A32,[1]Sheet1!$C:$C,1,0)</f>
-        <v>MSFT</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>SMFG</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" t="str">
         <f>VLOOKUP(A33,[1]Sheet1!$C:$C,1,0)</f>
-        <v>MC.PA</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>AAPL</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" t="str">
         <f>VLOOKUP(A34,[1]Sheet1!$C:$C,1,0)</f>
-        <v>VWO</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>VBTC.DE</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" t="str">
         <f>VLOOKUP(A35,[1]Sheet1!$C:$C,1,0)</f>
-        <v>ACI</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>BATT.AS</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B36" t="str">
         <f>VLOOKUP(A36,[1]Sheet1!$C:$C,1,0)</f>
-        <v>AMAT</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>SQM</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B37" t="str">
         <f>VLOOKUP(A37,[1]Sheet1!$C:$C,1,0)</f>
-        <v>KMB</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>NEE</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B38" t="str">
         <f>VLOOKUP(A38,[1]Sheet1!$C:$C,1,0)</f>
-        <v>BATT.AS</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>LEVI</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B39" t="str">
         <f>VLOOKUP(A39,[1]Sheet1!$C:$C,1,0)</f>
-        <v>VHYD.L</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>NVDA</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B40" t="str">
         <f>VLOOKUP(A40,[1]Sheet1!$C:$C,1,0)</f>
-        <v>EXC</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>CIB</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B41" t="str">
         <f>VLOOKUP(A41,[1]Sheet1!$C:$C,1,0)</f>
-        <v>LEVI</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>SPY</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B42" t="str">
         <f>VLOOKUP(A42,[1]Sheet1!$C:$C,1,0)</f>
-        <v>SPY</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>AVGO</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B43" t="str">
         <f>VLOOKUP(A43,[1]Sheet1!$C:$C,1,0)</f>
-        <v>ING</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>COIN</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B44" t="str">
         <f>VLOOKUP(A44,[1]Sheet1!$C:$C,1,0)</f>
-        <v>PEP</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>FLOA.L</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B45" t="str">
         <f>VLOOKUP(A45,[1]Sheet1!$C:$C,1,0)</f>
-        <v>BOTZ.L</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>KMB</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B46" t="str">
         <f>VLOOKUP(A46,[1]Sheet1!$C:$C,1,0)</f>
-        <v>SQM</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B47" t="str">
         <f>VLOOKUP(A47,[1]Sheet1!$C:$C,1,0)</f>
-        <v>AAPL</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>MA</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B48" t="str">
         <f>VLOOKUP(A48,[1]Sheet1!$C:$C,1,0)</f>
-        <v>PANW</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>JPY=X</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B49" t="str">
         <f>VLOOKUP(A49,[1]Sheet1!$C:$C,1,0)</f>
-        <v>INGR</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>FSLR</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B50" t="str">
         <f>VLOOKUP(A50,[1]Sheet1!$C:$C,1,0)</f>
-        <v>TSM</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>V</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B51" t="str">
         <f>VLOOKUP(A51,[1]Sheet1!$C:$C,1,0)</f>
-        <v>VBTC.DE</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>VHYD.L</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B52" t="str">
         <f>VLOOKUP(A52,[1]Sheet1!$C:$C,1,0)</f>
-        <v>C</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>JKS</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B53" t="str">
         <f>VLOOKUP(A53,[1]Sheet1!$C:$C,1,0)</f>
-        <v>FLOA.L</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>SHELL.AS</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B54" t="str">
         <f>VLOOKUP(A54,[1]Sheet1!$C:$C,1,0)</f>
-        <v>SMFG</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>WMT</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B55" t="str">
         <f>VLOOKUP(A55,[1]Sheet1!$C:$C,1,0)</f>
-        <v>BAP</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>BCS</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B56" t="str">
         <f>VLOOKUP(A56,[1]Sheet1!$C:$C,1,0)</f>
-        <v>FSLR</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>QCOM</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B57" t="str">
         <f>VLOOKUP(A57,[1]Sheet1!$C:$C,1,0)</f>
-        <v>DAR</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>MAXN</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B58" t="str">
         <f>VLOOKUP(A58,[1]Sheet1!$C:$C,1,0)</f>
-        <v>BND</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
+        <v>INGR</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B59" t="str">
         <f>VLOOKUP(A59,[1]Sheet1!$C:$C,1,0)</f>
         <v>MO</v>
       </c>
     </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>59</v>
+      </c>
+      <c r="B60" t="str">
+        <f>VLOOKUP(A60,[1]Sheet1!$C:$C,1,0)</f>
+        <v>GILD</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>60</v>
+      </c>
+      <c r="B61" t="str">
+        <f>VLOOKUP(A61,[1]Sheet1!$C:$C,1,0)</f>
+        <v>DUK</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>61</v>
+      </c>
+      <c r="B62" t="str">
+        <f>VLOOKUP(A62,[1]Sheet1!$C:$C,1,0)</f>
+        <v>^VIX</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>62</v>
+      </c>
+      <c r="B63" t="str">
+        <f>VLOOKUP(A63,[1]Sheet1!$C:$C,1,0)</f>
+        <v>BND</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>63</v>
+      </c>
+      <c r="B64" t="str">
+        <f>VLOOKUP(A64,[1]Sheet1!$C:$C,1,0)</f>
+        <v>VWO</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>64</v>
+      </c>
+      <c r="B65" t="str">
+        <f>VLOOKUP(A65,[1]Sheet1!$C:$C,1,0)</f>
+        <v>PHGP.L</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>65</v>
+      </c>
+      <c r="B66" t="str">
+        <f>VLOOKUP(A66,[1]Sheet1!$C:$C,1,0)</f>
+        <v>SDIA.L</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B59" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="#N/A"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Stock Selection/tickers_update.xlsx
+++ b/Stock Selection/tickers_update.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A67"/>
+  <dimension ref="A1:A70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,332 +438,332 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SMFG</t>
+          <t>ING</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>SMFG</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>MA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DUK</t>
+          <t>JPY=X</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GIS</t>
+          <t>VHYD.L</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JKS</t>
+          <t>BLX</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>WMT</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>QCOM</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>GOOGL</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>US30</t>
+          <t>^VIX</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BTCE.DE</t>
+          <t>MXN=X</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>PHGP.L</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>^VIX</t>
+          <t>BBVA</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SQM</t>
+          <t>INGR</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>BBAR</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>PANW</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BBVA</t>
+          <t>VBTC.DE</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>LEVI</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>MSFT</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JPY=X</t>
+          <t>FSLR</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MC.PA</t>
+          <t>APA</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>KMB</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>ASML</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BAP</t>
+          <t>COIN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BOTZ.L</t>
+          <t>ACI</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SHELL.AS</t>
+          <t>SDIA.L</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>BATT.AS</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PHGP.L</t>
+          <t>BND</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>DAR</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SLV</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>TSM</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>SQM</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>DUK</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>BAP</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SLV</t>
+          <t>EXC</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>VBTC.DE</t>
+          <t>VWO</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>AMAT</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>MAXN</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>JKS</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>AVGO</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>EQNR</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>AAPL</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>US30</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>GILD</t>
         </is>
       </c>
     </row>
@@ -777,119 +777,140 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>IAPD.AS</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>BTCE.DE</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>YUM</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>CIB</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>PEP</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>OXY</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>AEP</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>LEVI</t>
+          <t>V</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>MC.PA</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>FLOA.L</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>BCS</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>AGIO</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MAXN</t>
+          <t>BOTZ.L</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>WMT</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>GC=F</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BBAR</t>
+          <t>SHELL.AS</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>NEE</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>YPF</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>GIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>NVDA</t>
         </is>
       </c>
     </row>

--- a/Stock Selection/tickers_update.xlsx
+++ b/Stock Selection/tickers_update.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A70"/>
+  <dimension ref="A1:A71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,479 +438,486 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>GIS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SMFG</t>
+          <t>ACI</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>BAP</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JPY=X</t>
+          <t>ASML.AS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>PEP</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BLX</t>
+          <t>VWO</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PHGP.L</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>V</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>SQM</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>WMT</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>^VIX</t>
+          <t>GILD</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>MC.PA</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PHGP.L</t>
+          <t>ING</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BBVA</t>
+          <t>NEE</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>AEP</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BBAR</t>
+          <t>BTCE.DE</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>BATT.AS</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>VBTC.DE</t>
+          <t>BND</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LEVI</t>
+          <t>BBAR</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>APA</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>KMB</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>MAXN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>^VIX</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>TSM</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>YUM</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>LEVI</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>FSLR</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>PANW</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>EQNR</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>BCS</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>QCOM</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SLV</t>
+          <t>ASML</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>GOOGL</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SQM</t>
+          <t>JKS</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BBVA</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DUK</t>
+          <t>MXN=X</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BAP</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>DUK</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>VBTC.DE</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>JPY=X</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MAXN</t>
+          <t>AVGO</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>JKS</t>
+          <t>SHELL.AS</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>COIN</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>SMFG</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>MA</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>US30</t>
+          <t>AGIO</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>BOTZ.L</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>DAR</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>IAPD.AS</t>
+          <t>VHYD.L</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BTCE.DE</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>FLOA.L</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>BLX</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>OXY</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>CIB</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>SDIA.L</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>US30</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MC.PA</t>
+          <t>MO</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>EXC</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>MSFT</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>AAPL</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BOTZ.L</t>
+          <t>SPY</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>IAPD.AS</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>AMAT</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SHELL.AS</t>
+          <t>NVDA</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>INGR</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>SLV</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>GIS</t>
+          <t>YPF</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>TTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>GC=F</t>
         </is>
       </c>
     </row>

--- a/Stock Selection/tickers_update.xlsx
+++ b/Stock Selection/tickers_update.xlsx
@@ -438,66 +438,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GIS</t>
+          <t>SDIA.L</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>VHYD.L</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BAP</t>
+          <t>ASML.AS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>BAP</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>AMAT</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PHGP.L</t>
+          <t>CIB</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>^VIX</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>MSFT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SQM</t>
+          <t>JPY=X</t>
         </is>
       </c>
     </row>
@@ -511,77 +515,73 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>TSM</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MC.PA</t>
+          <t>PEP</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>BLX</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>COIN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>BTCE.DE</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BTCE.DE</t>
+          <t>BATT.AS</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>APA</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>YPF</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>BBAR</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>ASML</t>
         </is>
       </c>
     </row>
@@ -595,105 +595,105 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>^VIX</t>
+          <t>MXN=X</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>SLV</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>BBAR</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LEVI</t>
+          <t>NEE</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>YUM</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>FLOA.L</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>DAR</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>JKS</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>AGIO</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>BBVA</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>SQM</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>JKS</t>
+          <t>INGR</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BBVA</t>
+          <t>BOTZ.L</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>GILD</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>MC.PA</t>
         </is>
       </c>
     </row>
@@ -707,35 +707,35 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>VBTC.DE</t>
+          <t>NVDA</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>JPY=X</t>
+          <t>ACI</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>AAPL</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SHELL.AS</t>
+          <t>IAPD.AS</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>OXY</t>
         </is>
       </c>
     </row>
@@ -749,175 +749,175 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>BND</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>EXC</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BOTZ.L</t>
+          <t>VBTC.DE</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>KMB</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>LEVI</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AEP</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>EQNR</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BLX</t>
+          <t>SPY</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>BCS</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>FSLR</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>ING</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>US30</t>
+          <t>PHGP.L</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>US30</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>MO</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>V</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>AVGO</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>GC=F</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>IAPD.AS</t>
+          <t>MA</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>GIS</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>QCOM</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>PANW</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SLV</t>
+          <t>SHELL.AS</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>VWO</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>GOOGL</t>
         </is>
       </c>
     </row>

--- a/Stock Selection/tickers_update.xlsx
+++ b/Stock Selection/tickers_update.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A71"/>
+  <dimension ref="A1:A88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,486 +438,605 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>BCS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>EXC</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>MXN=X</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>AVGO</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BAP</t>
+          <t>HCA</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>NVDA</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>VWO</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>^VIX</t>
+          <t>WMT</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>US30</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JPY=X</t>
+          <t>HON</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>APA</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>YUM</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>DUK</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BLX</t>
+          <t>VIST</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>BVN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BTCE.DE</t>
+          <t>SEDG</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>VHYD.L</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>SMFG</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>GOOGL</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>TSM</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>PHGP.L</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MAXN</t>
+          <t>SLV</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>FSLR</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SLV</t>
+          <t>EQNR</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BBAR</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>ACI</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>SGLD.L</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>VALE</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>BOTZ.L</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>JKS</t>
+          <t>BAP</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>EXXW.DE</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BBVA</t>
+          <t>YPF</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SQM</t>
+          <t>TTE</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>FLOA.L</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BOTZ.L</t>
+          <t>^VIX</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>BLX</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MC.PA</t>
+          <t>QCOM</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DUK</t>
+          <t>ING</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>NEE</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>OXY</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>ALB</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>IAPD.AS</t>
+          <t>BBAR</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>G.MI</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SMFG</t>
+          <t>AEP</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>PANW</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>MAXN</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>VBTC.DE</t>
+          <t>AMAT</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>GC=F</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>LEVI</t>
+          <t>CIG</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>SYY</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>BND</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>IAPD.AS</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>BCS</t>
-        </is>
-      </c>
+      <c r="A55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>AAPL</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>GIS</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PHGP.L</t>
+          <t>BTCE.DE</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>US30</t>
+          <t>SQM</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>GILD</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>WEN</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>ASML.AS</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>GC=F</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>NDIA.L</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>GIS</t>
+          <t>KMB</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>COIN</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>INGR</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SHELL.AS</t>
+          <t>MA</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>VBTC.DE</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>JPY=X</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>SDIA.L</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>BBVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>JKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>BATT.AS</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>SHELL.AS</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>LEVI</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>CSIQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>MC.PA</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>UEC</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>DAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>AGIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>ASML</t>
         </is>
       </c>
     </row>
